--- a/baza_pociagow_linia73.xlsx
+++ b/baza_pociagow_linia73.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="baza_pociagow_linia73" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="baza_pociagow_linia73" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,10 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,39 +28,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00000000"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-        <bgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -67,35 +45,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00AAAAAA"/>
-      </left>
-      <right style="thin">
-        <color rgb="00AAAAAA"/>
-      </right>
-      <top style="thin">
-        <color rgb="00AAAAAA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00AAAAAA"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -461,88 +417,83 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>czasPojawienia</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>typPociagu</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>kategoria</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>liczbaWagonow</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>liczbaPasazerow</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>planowanyOdjazd</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>wartosc</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Unnamed: 8</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="n">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="n">
         <v>46124.25208333333</v>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Regio</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Zatrzymujacy</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2" s="2" t="n">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
         <v>40</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="1" t="n">
         <v>46124.25416666667</v>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Z_Poludnia</t>
         </is>
@@ -552,32 +503,32 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="n">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="n">
         <v>46124.26388888889</v>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Regio</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Zatrzymujacy</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>3</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" t="n">
         <v>75</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="1" t="n">
         <v>46124.26666666667</v>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Z_Poludnia</t>
         </is>
@@ -587,32 +538,32 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="1" t="n">
         <v>46124.28125</v>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Regio</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Zatrzymujacy</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="2" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
         <v>55</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="1" t="n">
         <v>46124.28402777778</v>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Z_Poludnia</t>
         </is>
@@ -622,32 +573,32 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="1" t="n">
         <v>46124.29513888889</v>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Regio</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Zatrzymujacy</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" s="2" t="n">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
         <v>85</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="1" t="n">
         <v>46124.29791666667</v>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Z_Poludnia</t>
         </is>
@@ -657,32 +608,32 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="1" t="n">
         <v>46124.31111111111</v>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Regio</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Zatrzymujacy</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" t="n">
         <v>120</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="1" t="n">
         <v>46124.31388888889</v>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Z_Poludnia</t>
         </is>
@@ -692,32 +643,32 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="1" t="n">
         <v>46124.32638888889</v>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Regio</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Zatrzymujacy</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" s="2" t="n">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
         <v>65</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="1" t="n">
         <v>46124.32916666667</v>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Z_Poludnia</t>
         </is>
@@ -727,32 +678,32 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="1" t="n">
         <v>46124.34166666667</v>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Regio</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Zatrzymujacy</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" t="n">
         <v>100</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="1" t="n">
         <v>46124.34444444445</v>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Z_Poludnia</t>
         </is>
@@ -762,32 +713,32 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="1" t="n">
         <v>46124.35763888889</v>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Regio</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Zatrzymujacy</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" s="2" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
         <v>50</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" s="1" t="n">
         <v>46124.36041666667</v>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Z_Poludnia</t>
         </is>
@@ -797,32 +748,32 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="1" t="n">
         <v>46124.375</v>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Regio</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Zatrzymujacy</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="2" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
         <v>40</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" s="1" t="n">
         <v>46124.37777777778</v>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Z_Poludnia</t>
         </is>
@@ -832,32 +783,32 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="1" t="n">
         <v>46124.39583333334</v>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Regio</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Zatrzymujacy</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F11" t="n">
         <v>70</v>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="G11" s="1" t="n">
         <v>46124.39861111111</v>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Z_Poludnia</t>
         </is>
@@ -867,32 +818,32 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="1" t="n">
         <v>46124.41666666666</v>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Regio</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Zatrzymujacy</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="2" t="n">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
         <v>45</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" s="1" t="n">
         <v>46124.41944444444</v>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Z_Poludnia</t>
         </is>
@@ -902,32 +853,32 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" s="1" t="n">
         <v>46124.25972222222</v>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Regio</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Zatrzymujacy</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="2" t="n">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
         <v>35</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" s="1" t="n">
         <v>46124.2625</v>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Z_Polnocy</t>
         </is>
@@ -937,32 +888,32 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="1" t="n">
         <v>46124.28472222222</v>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Regio</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Zatrzymujacy</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="2" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
         <v>60</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" s="1" t="n">
         <v>46124.2875</v>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Z_Polnocy</t>
         </is>
@@ -972,32 +923,32 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" s="1" t="n">
         <v>46124.30208333334</v>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Regio</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Zatrzymujacy</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
         <v>3</v>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="F15" t="n">
         <v>90</v>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="G15" s="1" t="n">
         <v>46124.30486111111</v>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Z_Polnocy</t>
         </is>
@@ -1007,32 +958,32 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="1" t="n">
         <v>46124.31944444445</v>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Regio</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Zatrzymujacy</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" s="2" t="n">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
         <v>70</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" s="1" t="n">
         <v>46124.32222222222</v>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Z_Polnocy</t>
         </is>
@@ -1042,32 +993,32 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B17" s="1" t="n">
         <v>46124.33680555555</v>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Regio</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Zatrzymujacy</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F17" s="2" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
         <v>55</v>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="G17" s="1" t="n">
         <v>46124.33958333333</v>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Z_Polnocy</t>
         </is>
@@ -1077,32 +1028,32 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="1" t="n">
         <v>46124.35277777778</v>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Regio</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Zatrzymujacy</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="F18" t="n">
         <v>80</v>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="G18" s="1" t="n">
         <v>46124.35555555556</v>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Z_Polnocy</t>
         </is>
@@ -1112,32 +1063,32 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B19" s="1" t="n">
         <v>46124.37152777778</v>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Regio</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Zatrzymujacy</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" s="2" t="n">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
         <v>45</v>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="G19" s="1" t="n">
         <v>46124.37430555555</v>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Z_Polnocy</t>
         </is>
@@ -1147,32 +1098,32 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" s="1" t="n">
         <v>46124.38888888889</v>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Regio</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Zatrzymujacy</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F20" s="2" t="n">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
         <v>35</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" s="1" t="n">
         <v>46124.39166666667</v>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Z_Polnocy</t>
         </is>
@@ -1182,37 +1133,562 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" s="1" t="n">
         <v>46124.40972222222</v>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Regio</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Zatrzymujacy</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="n">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
         <v>3</v>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="F21" t="n">
         <v>60</v>
       </c>
-      <c r="G21" s="3" t="n">
+      <c r="G21" s="1" t="n">
         <v>46124.4125</v>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Z_Polnocy</t>
         </is>
       </c>
       <c r="I21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>46124.4375</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>45</v>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>46124.44027777778</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Z_Poludnia</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>46124.45833333334</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>70</v>
+      </c>
+      <c r="G23" s="1" t="n">
+        <v>46124.46111111111</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Z_Poludnia</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>46124.47916666666</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>50</v>
+      </c>
+      <c r="G24" s="1" t="n">
+        <v>46124.48194444444</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Z_Poludnia</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>46124.5</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>80</v>
+      </c>
+      <c r="G25" s="1" t="n">
+        <v>46124.50277777778</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Z_Poludnia</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>46124.52083333334</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>40</v>
+      </c>
+      <c r="G26" s="1" t="n">
+        <v>46124.52361111111</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Z_Poludnia</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>46124.54166666666</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="n">
+        <v>65</v>
+      </c>
+      <c r="G27" s="1" t="n">
+        <v>46124.54444444444</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Z_Poludnia</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>46124.5625</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>55</v>
+      </c>
+      <c r="G28" s="1" t="n">
+        <v>46124.56527777778</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Z_Poludnia</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>46124.43055555555</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>40</v>
+      </c>
+      <c r="G29" s="1" t="n">
+        <v>46124.43333333333</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Z_Polnocy</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>46124.45138888889</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" t="n">
+        <v>60</v>
+      </c>
+      <c r="G30" s="1" t="n">
+        <v>46124.45416666667</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Z_Polnocy</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>46124.47222222222</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>50</v>
+      </c>
+      <c r="G31" s="1" t="n">
+        <v>46124.475</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Z_Polnocy</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>46124.49305555555</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>75</v>
+      </c>
+      <c r="G32" s="1" t="n">
+        <v>46124.49583333333</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Z_Polnocy</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>46124.51388888889</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>35</v>
+      </c>
+      <c r="G33" s="1" t="n">
+        <v>46124.51666666667</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Z_Polnocy</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>46124.53472222222</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" t="n">
+        <v>55</v>
+      </c>
+      <c r="G34" s="1" t="n">
+        <v>46124.5375</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Z_Polnocy</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>46124.55555555555</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>45</v>
+      </c>
+      <c r="G35" s="1" t="n">
+        <v>46124.55833333333</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Z_Polnocy</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>46124.57638888889</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Regio</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Zatrzymujacy</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>3</v>
+      </c>
+      <c r="F36" t="n">
+        <v>65</v>
+      </c>
+      <c r="G36" s="1" t="n">
+        <v>46124.57916666667</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Z_Polnocy</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
         <v>1</v>
       </c>
     </row>
